--- a/reports/ASX_Strong_Buy_Screener_2026-10-27.xlsx
+++ b/reports/ASX_Strong_Buy_Screener_2026-10-27.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report generated: 2026-10-27 00:00 </t>
+          <t xml:space="preserve">Report generated: 2026-10-27 23:55 </t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6.86</v>
+        <v>6.85</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>9.970000000000001</v>
@@ -926,13 +926,13 @@
         <v>4.88</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.0267</v>
+        <v>0.0263</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.0534</v>
+        <v>0.0526</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.1067</v>
+        <v>0.1052</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>27.44</v>
+        <v>28.54</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>5.72</v>
+        <v>5.71</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>2.53</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" s="5" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6.745</v>
+        <v>6.77</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>7.75</v>
@@ -1210,13 +1210,13 @@
         <v>6.52</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.0189</v>
+        <v>0.0171</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.0377</v>
+        <v>0.0342</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.0755</v>
+        <v>0.0684</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>39.68</v>
+        <v>39.82</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>11.55</v>
+        <v>11.59</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.26</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>39.34</v>
+        <v>39.28</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>45.49</v>
@@ -1277,13 +1277,13 @@
         <v>27.575</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.0289</v>
+        <v>0.0293</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.0578</v>
+        <v>0.0587</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.1156</v>
+        <v>0.1173</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>63.24</v>
+        <v>63.36</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>67.43000000000001</v>
@@ -1344,13 +1344,13 @@
         <v>44.18</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.0144</v>
+        <v>0.0139</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.0288</v>
+        <v>0.0278</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.0577</v>
+        <v>0.0557</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>26.8</v>
+        <v>26.62</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6.18</v>
+        <v>6.19</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>5.95</v>
+        <v>5.97</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.31</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>20.03</v>
+        <v>20.53</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>26.17</v>
@@ -1411,13 +1411,13 @@
         <v>19.28</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0506</v>
+        <v>0.0428</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.1013</v>
+        <v>0.0856</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.2026</v>
+        <v>0.1713</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>31.3</v>
+        <v>32.08</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>5.98</v>
+        <v>6.13</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0.92</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.375</v>
+        <v>0.395</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>0.95</v>
@@ -1478,13 +1478,13 @@
         <v>0.375</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1.1833</v>
+        <v>1.1108</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2.3667</v>
+        <v>2.2215</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>4.7333</v>
+        <v>4.443</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>-11.25</v>
+        <v>-11.85</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3.705</v>
+        <v>3.71</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5.235</v>
@@ -1551,13 +1551,13 @@
         <v>3.58</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.0242</v>
+        <v>0.0239</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.0484</v>
+        <v>0.0477</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.0969</v>
+        <v>0.0954</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>46.31</v>
+        <v>46.38</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>1.03</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>34.34</v>
+        <v>34.39</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>0.31</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>65.73999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>71.09999999999999</v>
@@ -1618,13 +1618,13 @@
         <v>51.2</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0.0188</v>
+        <v>0.0193</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.0385</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.0751</v>
+        <v>0.077</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>18.73</v>
+        <v>18.56</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>1.29</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2.455</v>
+        <v>2.46</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>2.665</v>
@@ -1685,13 +1685,13 @@
         <v>1.14</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.0081</v>
+        <v>0.0076</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.0162</v>
+        <v>0.0151</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.0324</v>
+        <v>0.0303</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>30.69</v>
+        <v>30.75</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>7.9</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>46.15</v>
+        <v>46.51</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>46.77</v>
@@ -1752,13 +1752,13 @@
         <v>25.05</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>-0.0363</v>
+        <v>-0.0383</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>-0.0726</v>
+        <v>-0.0767</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-0.1453</v>
+        <v>-0.1533</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>21.47</v>
+        <v>21.84</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.37</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>39.57</v>
+        <v>39.92</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>41</v>
@@ -1819,13 +1819,13 @@
         <v>33.36</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.019</v>
+        <v>-0.021</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.038</v>
+        <v>-0.0421</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.076</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>20.09</v>
+        <v>20.26</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>11.425</v>
+        <v>11.38</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>11.62</v>
@@ -1890,13 +1890,13 @@
         <v>8.445</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>-0.0363</v>
+        <v>-0.0355</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>-0.0726</v>
+        <v>-0.0709</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.1452</v>
+        <v>-0.1419</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>71.41</v>
+        <v>71.12</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>5.07</v>
+        <v>5.05</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>5.26</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>19.67</v>
+        <v>19.25</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>35.01</v>
@@ -1957,13 +1957,13 @@
         <v>17.56</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.1555</v>
+        <v>0.1698</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.3109</v>
+        <v>0.3395</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>21.15</v>
+        <v>23.48</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="M17" s="9" t="n">
         <v>1.73</v>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>16.95</v>
+        <v>16.705</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>37.49</v>
@@ -2099,13 +2099,13 @@
         <v>16.21</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.0761</v>
+        <v>0.0809</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.1523</v>
+        <v>0.1619</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.3046</v>
+        <v>0.3237</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>15.55</v>
+        <v>15.61</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>6.68</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2157,22 +2157,22 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>2.635</v>
+        <v>2.63</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3.95</v>
+        <v>3.905</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>1.985</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.0407</v>
+        <v>0.0413</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.0814</v>
+        <v>0.0825</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.1628</v>
+        <v>0.1651</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>7.98</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0.82</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.35</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>65.285</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>66.06</v>
@@ -2233,13 +2233,13 @@
         <v>44.3</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.0185</v>
+        <v>-0.0172</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.0371</v>
+        <v>-0.0343</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.0742</v>
+        <v>-0.0687</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -2247,13 +2247,13 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>26.43</v>
+        <v>26.28</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>10.21</v>
+        <v>10.15</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.12</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>29.25</v>
+        <v>29.23</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>40.28</v>
@@ -2300,13 +2300,13 @@
         <v>22.08</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.051</v>
+        <v>0.0512</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.102</v>
+        <v>0.1024</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2039</v>
+        <v>0.2047</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>37.5</v>
+        <v>37.47</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>2.03</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>3.845</v>
+        <v>3.835</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>4.42</v>
@@ -2442,13 +2442,13 @@
         <v>3.37</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0081</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>-0.0174</v>
+        <v>-0.0161</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-0.0347</v>
+        <v>-0.0322</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="J24" s="5" t="n">
-        <v>18.31</v>
+        <v>18.26</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>1.64</v>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.83</v>
+        <v>0.895</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>0.355</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.0115</v>
+        <v>-0.0288</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.023</v>
+        <v>-0.0576</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.046</v>
+        <v>-0.1153</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="J25" s="5" t="n">
-        <v>18.68</v>
+        <v>20.14</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>0.76</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>10.41</v>
+        <v>10.475</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>13.11</v>
@@ -2576,13 +2576,13 @@
         <v>9.81</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>-0.0045</v>
+        <v>-0.0061</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>-0.0091</v>
+        <v>-0.0121</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>-0.0182</v>
+        <v>-0.0243</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>16.79</v>
+        <v>16.63</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>6.18</v>
+        <v>6.27</v>
       </c>
       <c r="D27" s="10" t="n">
         <v>6.89</v>
@@ -2645,13 +2645,13 @@
         <v>5</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.0363</v>
+        <v>0.0322</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.0725</v>
+        <v>0.0643</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.145</v>
+        <v>0.1286</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -2659,13 +2659,13 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>34.33</v>
+        <v>34.83</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="M27" s="9" t="n">
         <v>0.47</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Q27" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>56.53</v>
+        <v>58.49</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>68.77</v>
@@ -2712,13 +2712,13 @@
         <v>40.175</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.0134</v>
+        <v>0.0041</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0.0268</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.0535</v>
+        <v>0.0165</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>19.63</v>
+        <v>19.69</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>4.89</v>
+        <v>5.06</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>0.5</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:55</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>6.82</v>
+        <v>6.85</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>7.48</v>
@@ -3004,13 +3004,13 @@
         <v>5.91</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>-0.0192</v>
+        <v>-0.0202</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>-0.0384</v>
+        <v>-0.0404</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>-0.0767</v>
+        <v>-0.0808</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="J32" s="5" t="n">
-        <v>18.43</v>
+        <v>19.03</v>
       </c>
       <c r="K32" s="5" t="n">
         <v>0.78</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.912</v>
+        <v>0.92</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>1.335</v>
@@ -3073,13 +3073,13 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0381</v>
+        <v>0.0356</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.0762</v>
+        <v>0.0711</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.1523</v>
+        <v>0.1423</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="J33" s="5" t="n">
-        <v>7.6</v>
+        <v>7.67</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
@@ -3117,74 +3117,74 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>BRG</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Breville Group Limited</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n">
-        <v>30.65</v>
-      </c>
-      <c r="D34" s="10" t="n">
+      <c r="C34" s="6" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>35.48</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="6" t="n">
         <v>25.41</v>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>0.0426</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>0.0851</v>
-      </c>
-      <c r="H34" s="11" t="n">
-        <v>0.1702</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>32.61</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="M34" s="9" t="n">
+      <c r="F34" s="7" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M34" s="5" t="n">
         <v>0.14</v>
       </c>
-      <c r="N34" s="12" t="inlineStr">
+      <c r="N34" s="8" t="inlineStr">
         <is>
           <t>2026: $1,810.9M | 2025: $1,696.6M | 2024: $1,530.0M | 2023: $1,478.6M</t>
         </is>
       </c>
-      <c r="O34" s="12" t="inlineStr">
+      <c r="O34" s="8" t="inlineStr">
         <is>
           <t>2026: $138.1M | 2025: $135.9M | 2024: $118.5M | 2023: $110.2M</t>
         </is>
       </c>
-      <c r="P34" s="12" t="inlineStr">
+      <c r="P34" s="8" t="inlineStr">
         <is>
           <t>Breville Group Limited engages in the design, development, marketing, and distribution of small electrical kitchen appliances in the Americas, the Asia Pacific, Europe, the Middle East, and Africa. It offers appliances for the kitchen, such as slow cookers, kettles, and fry pans, as well as living room, laundry and bedroom, including irons, vacuums, heaters, electric blankets, and fans. The com...</t>
         </is>
       </c>
-      <c r="Q34" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-27 00:00</t>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>33.32</v>
+        <v>33.77</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>35.26</v>
@@ -3209,13 +3209,13 @@
         <v>20.46</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0194</v>
+        <v>0.0187</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.0389</v>
+        <v>0.0375</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -3223,10 +3223,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>17.91</v>
+        <v>18.76</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>4.12</v>
@@ -3278,13 +3278,13 @@
         <v>3.395</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.0152</v>
+        <v>0.0137</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.0303</v>
+        <v>0.0274</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0.0606</v>
+        <v>0.0547</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>6.26</v>
+        <v>6.53</v>
       </c>
       <c r="K36" s="5" t="n">
         <v>0.84</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>13.4</v>
+        <v>13.47</v>
       </c>
       <c r="M36" s="5" t="n">
         <v>0.23</v>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>21.42</v>
+        <v>21.29</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>25.56</v>
@@ -3345,13 +3345,13 @@
         <v>16.18</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0045</v>
+        <v>0.0056</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0111</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.0179</v>
+        <v>0.0223</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3359,13 +3359,13 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>21</v>
+        <v>21.08</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>6.22</v>
+        <v>6.18</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0.9399999999999999</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>24.085</v>
+        <v>24.39</v>
       </c>
       <c r="D38" s="10" t="n">
         <v>37.45</v>
@@ -3412,13 +3412,13 @@
         <v>21.2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.0959</v>
+        <v>0.0915</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.1917</v>
+        <v>0.1831</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.3834</v>
+        <v>0.3661</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -3426,13 +3426,13 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>29.37</v>
+        <v>29.39</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>7.29</v>
+        <v>7.38</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>0.57</v>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>161.66</v>
+        <v>163.265</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>185.59</v>
@@ -3479,13 +3479,13 @@
         <v>146.98</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.0558</v>
+        <v>-0.0577</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.1117</v>
+        <v>-0.1155</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.2234</v>
+        <v>-0.231</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="J39" s="5" t="n">
-        <v>24.91</v>
+        <v>25.23</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3539,22 +3539,22 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>14.57</v>
+        <v>15.16</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>15.32</v>
+        <v>15.34</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>9.5</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0326</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0.0866</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0.1732</v>
+        <v>0.1303</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>9.52</v>
+        <v>9.84</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>0.54</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>11.965</v>
+        <v>11.85</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>11.97</v>
@@ -3690,13 +3690,13 @@
         <v>7.25</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>-0.0105</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>-0.0211</v>
+        <v>-0.0164</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>-0.0421</v>
+        <v>-0.0328</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="J42" s="5" t="n">
-        <v>20.99</v>
+        <v>20.79</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>2.08</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>19.77</v>
+        <v>19.985</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>25.95</v>
@@ -3757,13 +3757,13 @@
         <v>17.49</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.0405</v>
+        <v>0.0374</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.081</v>
+        <v>0.0747</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.1619</v>
+        <v>0.1494</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="J43" s="5" t="n">
-        <v>22.21</v>
+        <v>22.71</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>11.53</v>
+        <v>11.65</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>0.26</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:00</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3815,22 +3815,22 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>6.685</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.1878</v>
+        <v>0.1631</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.3756</v>
+        <v>0.3263</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.7512</v>
+        <v>0.6525</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="M44" s="9" t="n">
         <v>0.88</v>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3.59</v>
@@ -3891,13 +3891,13 @@
         <v>2.68</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0444</v>
+        <v>0.0454</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.0887</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.1775</v>
+        <v>0.1817</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="J45" s="5" t="n">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="K45" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>6.86</v>
+        <v>6.84</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.5600000000000001</v>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>8.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>12.73</v>
@@ -3958,13 +3958,13 @@
         <v>7.59</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.0365</v>
+        <v>0.0349</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>0.0731</v>
+        <v>0.0699</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.1462</v>
+        <v>0.1398</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>22.82</v>
+        <v>22.95</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>2</v>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="Q46" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4016,22 +4016,22 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>3.11</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.035</v>
+        <v>0.0342</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0683</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0.1401</v>
+        <v>0.1367</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="J47" s="5" t="n">
-        <v>8.56</v>
+        <v>8.82</v>
       </c>
       <c r="K47" s="5" t="n">
         <v>0.71</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>12.41</v>
+        <v>12.45</v>
       </c>
       <c r="M47" s="5" t="n">
         <v>0.45</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>0.332</v>
+        <v>0.335</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>0.49</v>
@@ -4092,13 +4092,13 @@
         <v>0.315</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.1642</v>
+        <v>0.1604</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.3283</v>
+        <v>0.3209</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>0.6566</v>
+        <v>0.6418</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>6.64</v>
+        <v>6.7</v>
       </c>
       <c r="K48" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>0.51</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>8.49</v>
@@ -4159,13 +4159,13 @@
         <v>6.37</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0659</v>
+        <v>0.0664</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.1318</v>
+        <v>0.1329</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.2635</v>
+        <v>0.2658</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="J49" s="5" t="n">
-        <v>92.86</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>4.01</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>138.99</v>
+        <v>141.29</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>296.5</v>
@@ -4226,13 +4226,13 @@
         <v>88.73999999999999</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>-0.0048</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>-0.0095</v>
+        <v>-0.0175</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>-0.0191</v>
+        <v>-0.035</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
@@ -4240,13 +4240,13 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>61.77</v>
+        <v>62.8</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="M50" s="5" t="n">
         <v>0.12</v>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>24.04</v>
+        <v>24</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>24.75</v>
@@ -4293,13 +4293,13 @@
         <v>20.1</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.002</v>
+        <v>0.0024</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>0.004</v>
+        <v>0.0049</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.0081</v>
+        <v>0.0097</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="J51" s="5" t="n">
-        <v>30.05</v>
+        <v>29.63</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>0.71</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>42.92</v>
+        <v>42.88</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>43.79</v>
@@ -4360,13 +4360,13 @@
         <v>26.73</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>-0.0175</v>
+        <v>-0.0177</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>-0.035</v>
+        <v>-0.0354</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0708</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>27.16</v>
+        <v>27.31</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>7.64</v>
+        <v>7.63</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4420,22 +4420,22 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>3.62</v>
+        <v>3.665</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>3.34</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.0529</v>
+        <v>0.0492</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>0.1059</v>
+        <v>0.0984</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0.2117</v>
+        <v>0.1968</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="J53" s="5" t="n">
-        <v>5.32</v>
+        <v>5.47</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="M53" s="5" t="n">
         <v>0.54</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4487,22 +4487,22 @@
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>193.67</v>
+        <v>197.805</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>213.85</v>
+        <v>199</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>90</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>-0.0095</v>
+        <v>-0.014</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>-0.019</v>
+        <v>-0.0279</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>-0.0381</v>
+        <v>-0.0558</v>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
@@ -4510,13 +4510,13 @@
         </is>
       </c>
       <c r="J54" s="5" t="n">
-        <v>20.55</v>
+        <v>20.98</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>5.88</v>
+        <v>6.01</v>
       </c>
       <c r="M54" s="5" t="n">
         <v>0.67</v>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>3.39</v>
+        <v>3.63</v>
       </c>
       <c r="D55" s="6" t="n">
         <v>16.07</v>
@@ -4563,13 +4563,13 @@
         <v>1.97</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.1557</v>
+        <v>0.1289</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0.3115</v>
+        <v>0.2578</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.6229</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
@@ -4577,13 +4577,13 @@
         </is>
       </c>
       <c r="J55" s="5" t="n">
-        <v>28.25</v>
+        <v>27.92</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="M55" s="5" t="n">
         <v>5.76</v>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>7.11</v>
+        <v>7.28</v>
       </c>
       <c r="D56" s="10" t="n">
         <v>13.48</v>
@@ -4630,13 +4630,13 @@
         <v>6.62</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>0.3428</v>
+        <v>0.3289</v>
       </c>
       <c r="G56" s="11" t="n">
-        <v>0.6855</v>
+        <v>0.6579</v>
       </c>
       <c r="H56" s="11" t="n">
-        <v>1.3711</v>
+        <v>1.3157</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>10.77</v>
+        <v>10.55</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>3.82</v>
+        <v>3.91</v>
       </c>
       <c r="M56" s="9" t="n">
         <v>0.71</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>3</v>
+        <v>2.995</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>3.005</v>
@@ -4697,13 +4697,13 @@
         <v>2.14</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.005</v>
+        <v>0.0059</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.01</v>
+        <v>0.0117</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="J57" s="5" t="n">
-        <v>75</v>
+        <v>74.88</v>
       </c>
       <c r="K57" s="5" t="n">
         <v>2.23</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0.8</v>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>21.38</v>
+        <v>21.32</v>
       </c>
       <c r="D59" s="6" t="n">
         <v>24.58</v>
@@ -4839,13 +4839,13 @@
         <v>14.83</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0075</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.0164</v>
+        <v>-0.0151</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.0329</v>
+        <v>-0.0301</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="J59" s="5" t="n">
-        <v>14.99</v>
+        <v>14.95</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>0.99</v>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>6.995</v>
+        <v>7.08</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>8.654999999999999</v>
@@ -4906,13 +4906,13 @@
         <v>6.25</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.0279</v>
+        <v>0.0229</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.0558</v>
+        <v>0.0457</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>0.1115</v>
+        <v>0.0914</v>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
@@ -4920,13 +4920,13 @@
         </is>
       </c>
       <c r="J60" s="5" t="n">
-        <v>21.2</v>
+        <v>22.12</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="M60" s="5" t="n">
         <v>0.66</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>4.78</v>
@@ -4973,13 +4973,13 @@
         <v>3.67</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.0528</v>
+        <v>0.0422</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.1056</v>
+        <v>0.0844</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.2111</v>
+        <v>0.1687</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -4987,13 +4987,13 @@
         </is>
       </c>
       <c r="J61" s="5" t="n">
-        <v>12.45</v>
+        <v>12.5</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>14.35</v>
+        <v>14.87</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>8.470000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M61" s="5" t="n">
         <v>1</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>5.73</v>
+        <v>5.725</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>7.73</v>
@@ -5040,13 +5040,13 @@
         <v>5.3</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.0317</v>
+        <v>0.0319</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0.0633</v>
+        <v>0.0638</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>0.1267</v>
+        <v>0.1277</v>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="J62" s="5" t="n">
-        <v>10.42</v>
+        <v>10.6</v>
       </c>
       <c r="K62" s="5" t="n">
         <v>0.62</v>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>6.19</v>
+        <v>6.13</v>
       </c>
       <c r="D63" s="6" t="n">
         <v>7.77</v>
@@ -5107,13 +5107,13 @@
         <v>4.96</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0171</v>
+        <v>0.0197</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0.0341</v>
+        <v>0.0393</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.0682</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -5121,13 +5121,13 @@
         </is>
       </c>
       <c r="J63" s="5" t="n">
-        <v>24.76</v>
+        <v>25.54</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="M63" s="5" t="n">
         <v>0.79</v>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>0.205</v>
+        <v>0.22</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>0.983</v>
@@ -5174,13 +5174,13 @@
         <v>0.193</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.5224</v>
+        <v>0.4697</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>1.0447</v>
+        <v>0.9394</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>2.0894</v>
+        <v>1.8788</v>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="J64" s="5" t="n">
-        <v>8.65</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="M64" s="5" t="n">
         <v>0.6899999999999999</v>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>11.58</v>
+        <v>12.01</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>17.75</v>
@@ -5241,13 +5241,13 @@
         <v>9.789999999999999</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0425</v>
+        <v>0.0321</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.0851</v>
+        <v>0.0641</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.1701</v>
+        <v>0.1282</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="J65" s="5" t="n">
-        <v>15.86</v>
+        <v>16.45</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>4.03</v>
+        <v>4.18</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>4.26</v>
+        <v>4.42</v>
       </c>
       <c r="M65" s="5" t="n">
         <v>0.25</v>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>2.61</v>
+        <v>2.645</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>3.44</v>
@@ -5308,13 +5308,13 @@
         <v>2.22</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.0457</v>
+        <v>0.0417</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.0835</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>0.1826</v>
+        <v>0.167</v>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="J66" s="5" t="n">
-        <v>16.31</v>
+        <v>16.53</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="L66" s="5" t="n">
         <v>0.47</v>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="C67" s="10" t="n">
-        <v>11.09</v>
+        <v>11.21</v>
       </c>
       <c r="D67" s="10" t="n">
         <v>16.56</v>
@@ -5375,13 +5375,13 @@
         <v>9.609999999999999</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0664</v>
       </c>
       <c r="G67" s="11" t="n">
-        <v>0.1427</v>
+        <v>0.1329</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>0.2855</v>
+        <v>0.2657</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>16.07</v>
+        <v>16.25</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="M67" s="9" t="n">
         <v>1.12</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Q67" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>14.56</v>
+        <v>14.715</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>23.38</v>
@@ -5442,13 +5442,13 @@
         <v>14.13</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.0151</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0.0369</v>
+        <v>0.0303</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>0.0738</v>
+        <v>0.0605</v>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
@@ -5456,13 +5456,13 @@
         </is>
       </c>
       <c r="J68" s="5" t="n">
-        <v>10.4</v>
+        <v>10.74</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="M68" s="5" t="n">
         <v>0.29</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>39.3</v>
+        <v>38.66</v>
       </c>
       <c r="D69" s="10" t="n">
         <v>40.15</v>
@@ -5509,13 +5509,13 @@
         <v>26.51</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>-0.0127</v>
+        <v>-0.0095</v>
       </c>
       <c r="G69" s="11" t="n">
-        <v>-0.0255</v>
+        <v>-0.019</v>
       </c>
       <c r="H69" s="11" t="n">
-        <v>-0.0509</v>
+        <v>-0.0379</v>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>56.14</v>
+        <v>56.03</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>13.44</v>
+        <v>13.22</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>10.02</v>
+        <v>9.85</v>
       </c>
       <c r="M69" s="9" t="n">
         <v>6.91</v>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="Q69" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>26.14</v>
+        <v>27.38</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>34.78</v>
+        <v>34.49</v>
       </c>
       <c r="E70" s="10" t="n">
         <v>24.56</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>0.0762</v>
+        <v>0.0614</v>
       </c>
       <c r="G70" s="11" t="n">
-        <v>0.1523</v>
+        <v>0.1228</v>
       </c>
       <c r="H70" s="11" t="n">
-        <v>0.3046</v>
+        <v>0.2456</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -5590,13 +5590,13 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>19.22</v>
+        <v>19.99</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>13.23</v>
+        <v>13.86</v>
       </c>
       <c r="M70" s="9" t="n">
         <v>0.24</v>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>6.615</v>
+        <v>6.47</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>9</v>
@@ -5643,27 +5643,27 @@
         <v>4.69</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>0.0204</v>
+        <v>0.0265</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>0.0409</v>
+        <v>0.053</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.0818</v>
+        <v>0.106</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J71" s="5" t="n">
-        <v>21.07</v>
+        <v>20.61</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="M71" s="5" t="n">
         <v>1.41</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>1.955</v>
+        <v>1.97</v>
       </c>
       <c r="D73" s="10" t="n">
         <v>2.68</v>
@@ -5785,13 +5785,13 @@
         <v>1.835</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>0.0876</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>0.1752</v>
+        <v>0.1701</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>0.3504</v>
+        <v>0.3401</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>16.29</v>
+        <v>16.42</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="M73" s="9" t="n">
         <v>0.84</v>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="Q73" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="J74" s="5" t="n">
-        <v>8.66</v>
+        <v>8.82</v>
       </c>
       <c r="K74" s="5" t="n">
         <v>0.85</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="D76" s="6" t="n">
         <v>1.07</v>
@@ -5994,13 +5994,13 @@
         <v>0.3</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>0.0624</v>
+        <v>0.0488</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.1248</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>0.2496</v>
+        <v>0.1953</v>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
@@ -6008,13 +6008,13 @@
         </is>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-129.41</v>
+        <v>-135.29</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="M76" s="5" t="n">
         <v>5.81</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>66.80500000000001</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="D77" s="10" t="n">
         <v>117.8</v>
@@ -6061,13 +6061,13 @@
         <v>58.71</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.0772</v>
+        <v>0.0591</v>
       </c>
       <c r="G77" s="11" t="n">
-        <v>0.1543</v>
+        <v>0.1182</v>
       </c>
       <c r="H77" s="11" t="n">
-        <v>0.3086</v>
+        <v>0.2364</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>46.07</v>
+        <v>47.78</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>9.85</v>
+        <v>10.43</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>10.99</v>
+        <v>11.64</v>
       </c>
       <c r="M77" s="9" t="n">
         <v>0.13</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="Q77" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>7.7</v>
@@ -6128,13 +6128,13 @@
         <v>3.93</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>0.0256</v>
+        <v>0.027</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>0.0513</v>
+        <v>0.054</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>0.1026</v>
+        <v>0.1079</v>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="J78" s="5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="K78" s="5" t="n">
         <v>1.05</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M78" s="5" t="n">
         <v>0.52</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Q78" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>8.81</v>
+        <v>8.73</v>
       </c>
       <c r="D79" s="6" t="n">
         <v>8.92</v>
@@ -6195,13 +6195,13 @@
         <v>6.39</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.0145</v>
+        <v>-0.0123</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.0289</v>
+        <v>-0.0246</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.0579</v>
+        <v>-0.0493</v>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="J79" s="5" t="n">
-        <v>17.64</v>
+        <v>17.48</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="M79" s="5" t="n">
         <v>0.41</v>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>6.43</v>
@@ -6262,13 +6262,13 @@
         <v>1.49</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>0.0365</v>
+        <v>0.0352</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>0.1459</v>
+        <v>0.1407</v>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="J80" s="5" t="n">
-        <v>55</v>
+        <v>55.25</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="L80" s="5" t="n">
         <v>0.77</v>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>4.935</v>
+        <v>5.285</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>10.05</v>
@@ -6404,13 +6404,13 @@
         <v>4.77</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0.1298</v>
+        <v>0.1047</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.2596</v>
+        <v>0.2093</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0.5192</v>
+        <v>0.4186</v>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
@@ -6418,13 +6418,13 @@
         </is>
       </c>
       <c r="J82" s="5" t="n">
-        <v>24.68</v>
+        <v>26.43</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>8.07</v>
+        <v>8.65</v>
       </c>
       <c r="M82" s="5" t="n">
         <v>0.75</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="Q82" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="C83" s="10" t="n">
-        <v>5.025</v>
+        <v>5.52</v>
       </c>
       <c r="D83" s="10" t="n">
         <v>8.69</v>
@@ -6471,13 +6471,13 @@
         <v>4.92</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>0.1448</v>
+        <v>0.1094</v>
       </c>
       <c r="G83" s="11" t="n">
-        <v>0.2896</v>
+        <v>0.2188</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.4375</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -6485,13 +6485,13 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>-18.71</v>
+        <v>-20.56</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="M83" s="9" t="n">
         <v>0.63</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Q83" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>5.05</v>
+        <v>5.01</v>
       </c>
       <c r="D84" s="10" t="n">
         <v>5.875</v>
@@ -6538,13 +6538,13 @@
         <v>3.49</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="G84" s="11" t="n">
-        <v>0.0041</v>
+        <v>0.0081</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0.0081</v>
+        <v>0.0162</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -6552,13 +6552,13 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>10.74</v>
+        <v>11.13</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="M84" s="9" t="n">
         <v>0.58</v>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="Q84" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>2.12</v>
+        <v>2.085</v>
       </c>
       <c r="D85" s="6" t="n">
         <v>2.69</v>
@@ -6605,13 +6605,13 @@
         <v>1.69</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.0168</v>
+        <v>0.0212</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0.0335</v>
+        <v>0.0425</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>23.56</v>
+        <v>23.17</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="L85" s="5" t="n">
         <v>0.24</v>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>3.675</v>
+        <v>3.75</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>4.42</v>
@@ -6672,27 +6672,27 @@
         <v>3.155</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>0.0425</v>
+        <v>0.0367</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0.0851</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>0.1702</v>
+        <v>0.1468</v>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>11.85</v>
+        <v>12.1</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M86" s="5" t="n">
         <v>0.67</v>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>5.68</v>
+        <v>5.64</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>10.38</v>
@@ -6814,13 +6814,13 @@
         <v>5.04</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>0.1376</v>
+        <v>0.1403</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0.2752</v>
+        <v>0.2807</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>0.5504</v>
+        <v>0.5614</v>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
@@ -6828,13 +6828,13 @@
         </is>
       </c>
       <c r="J88" s="5" t="n">
-        <v>11.59</v>
+        <v>11.75</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="M88" s="5" t="n">
         <v>0.41</v>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>73.26000000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="D90" s="6" t="n">
         <v>115.95</v>
@@ -6956,13 +6956,13 @@
         <v>64.18000000000001</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>0.0098</v>
+        <v>0.0138</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0.0196</v>
+        <v>0.0276</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>0.0392</v>
+        <v>0.0551</v>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
@@ -6970,13 +6970,13 @@
         </is>
       </c>
       <c r="J90" s="5" t="n">
-        <v>16.39</v>
+        <v>16.14</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>4.89</v>
+        <v>4.81</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="M90" s="5" t="n">
         <v>0.43</v>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="Q90" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>36.945</v>
+        <v>37.37</v>
       </c>
       <c r="D92" s="10" t="n">
         <v>44.12</v>
@@ -7098,13 +7098,13 @@
         <v>24.41</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>0.0453</v>
+        <v>0.0414</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>0.0906</v>
+        <v>0.0828</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>0.1812</v>
+        <v>0.1657</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -7112,13 +7112,13 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>99.84999999999999</v>
+        <v>101</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="M92" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="C93" s="10" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="D93" s="10" t="n">
         <v>5.25</v>
@@ -7165,13 +7165,13 @@
         <v>3.68</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.0809</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>0.1618</v>
+        <v>0.1719</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>0.3236</v>
+        <v>0.3438</v>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
@@ -7179,13 +7179,13 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>17.35</v>
+        <v>17.09</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="M93" s="9" t="n">
         <v>1.11</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="Q93" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7223,22 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="E94" s="6" t="n">
         <v>2.34</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>0.1181</v>
+        <v>0.1227</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0.2362</v>
+        <v>0.2454</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0.4725</v>
+        <v>0.4908</v>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>9.85</v>
+        <v>9.73</v>
       </c>
       <c r="K94" s="5" t="n">
         <v>0.42</v>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="Q94" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>11.285</v>
+        <v>12.335</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>22.37</v>
@@ -7374,13 +7374,13 @@
         <v>10.69</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0.1318</v>
+        <v>0.0993</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0.2636</v>
+        <v>0.1986</v>
       </c>
       <c r="H96" s="7" t="n">
-        <v>0.5272</v>
+        <v>0.3972</v>
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
@@ -7388,13 +7388,13 @@
         </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>49.07</v>
+        <v>53.63</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>11.61</v>
+        <v>12.7</v>
       </c>
       <c r="M96" s="5" t="n">
         <v>9.69</v>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>7.585</v>
+        <v>7.57</v>
       </c>
       <c r="D97" s="6" t="n">
         <v>11.55</v>
@@ -7441,13 +7441,13 @@
         <v>7.26</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.0265</v>
+        <v>0.027</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.0529</v>
+        <v>0.054</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.1058</v>
+        <v>0.108</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
@@ -7455,13 +7455,13 @@
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>14.59</v>
+        <v>15.45</v>
       </c>
       <c r="K97" s="5" t="n">
         <v>1.33</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="M97" s="5" t="n">
         <v>0.19</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>1.815</v>
+        <v>1.84</v>
       </c>
       <c r="D98" s="10" t="n">
         <v>2.46</v>
@@ -7508,13 +7508,13 @@
         <v>1.607</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>0.0337</v>
+        <v>0.0299</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0.0675</v>
+        <v>0.0598</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.135</v>
+        <v>0.1196</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -7522,13 +7522,13 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>10.68</v>
+        <v>10.82</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="M98" s="9" t="n">
         <v>0.42</v>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="Q98" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>43.06</v>
+        <v>45.16</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>74.94</v>
@@ -7575,13 +7575,13 @@
         <v>41.62</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.095</v>
+        <v>0.079</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0.1901</v>
+        <v>0.158</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.3801</v>
+        <v>0.316</v>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
@@ -7589,13 +7589,13 @@
         </is>
       </c>
       <c r="J99" s="5" t="n">
-        <v>7.94</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M99" s="5" t="n">
         <v>1.21</v>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>5.025</v>
+        <v>5.005</v>
       </c>
       <c r="D100" s="6" t="n">
         <v>5.31</v>
@@ -7642,13 +7642,13 @@
         <v>4.06</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>0.0015</v>
+        <v>0.0025</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0.003</v>
+        <v>0.0051</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>0.0061</v>
+        <v>0.0101</v>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="J100" s="5" t="n">
-        <v>21.85</v>
+        <v>21.76</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M100" s="5" t="n">
         <v>0.11</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>246.47</v>
+        <v>250.25</v>
       </c>
       <c r="D101" s="6" t="n">
         <v>267.905</v>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="D102" s="6" t="n">
         <v>3.98</v>
@@ -7784,13 +7784,13 @@
         <v>2.63</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>0.0146</v>
+        <v>0.0114</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>0.0293</v>
+        <v>0.0227</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>0.0585</v>
+        <v>0.0454</v>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="J102" s="5" t="n">
-        <v>12.76</v>
+        <v>12.92</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>40.35</v>
+        <v>40.25</v>
       </c>
       <c r="D103" s="6" t="n">
         <v>49.45</v>
@@ -7853,13 +7853,13 @@
         <v>35.48</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.0112</v>
+        <v>-0.0111</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.0225</v>
+        <v>-0.0222</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.045</v>
+        <v>-0.0444</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="J103" s="5" t="n">
-        <v>20.38</v>
+        <v>20.43</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>3.085</v>
+        <v>3.13</v>
       </c>
       <c r="D104" s="6" t="n">
         <v>4.66</v>
@@ -7924,13 +7924,13 @@
         <v>2.64</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>0.0645</v>
+        <v>0.06</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0.1291</v>
+        <v>0.12</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>0.2582</v>
+        <v>0.2401</v>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="J104" s="5" t="n">
-        <v>51.42</v>
+        <v>52.17</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="M104" s="5" t="n">
         <v>0.11</v>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="D105" s="6" t="n">
         <v>1.245</v>
@@ -7991,13 +7991,13 @@
         <v>0.613</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.221</v>
+        <v>0.216</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.4419</v>
+        <v>0.432</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.8838</v>
+        <v>0.8641</v>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="J105" s="5" t="n">
-        <v>6.8</v>
+        <v>6.88</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="L105" s="5" t="n">
         <v>0.48</v>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>6.57</v>
+        <v>6.55</v>
       </c>
       <c r="D106" s="6" t="n">
         <v>7.73</v>
@@ -8058,13 +8058,13 @@
         <v>5.79</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>0.0305</v>
+        <v>0.0314</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.0611</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="H106" s="7" t="n">
-        <v>0.1221</v>
+        <v>0.1255</v>
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="J106" s="5" t="n">
-        <v>17.76</v>
+        <v>17.24</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="M106" s="5" t="n">
         <v>0.2</v>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>24.84</v>
+        <v>25.76</v>
       </c>
       <c r="D108" s="6" t="n">
         <v>31.96</v>
@@ -8200,13 +8200,13 @@
         <v>17.07</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>0.0218</v>
+        <v>0.0121</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>0.0436</v>
+        <v>0.0242</v>
       </c>
       <c r="H108" s="7" t="n">
-        <v>0.0872</v>
+        <v>0.0484</v>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
@@ -8214,13 +8214,13 @@
         </is>
       </c>
       <c r="J108" s="5" t="n">
-        <v>20.87</v>
+        <v>21.83</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>4.64</v>
+        <v>4.82</v>
       </c>
       <c r="M108" s="5" t="n">
         <v>0.11</v>
@@ -8242,74 +8242,74 @@
       </c>
       <c r="Q108" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:01</t>
+          <t>2026-10-27 23:56</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>NUF</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>Nufarm Limited</t>
         </is>
       </c>
-      <c r="C109" s="6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="D109" s="6" t="n">
+      <c r="C109" s="10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D109" s="10" t="n">
         <v>3.37</v>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E109" s="10" t="n">
         <v>1.79</v>
       </c>
-      <c r="F109" s="7" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>0.0887</v>
-      </c>
-      <c r="H109" s="7" t="n">
-        <v>0.1773</v>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="K109" s="5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M109" s="5" t="n">
+      <c r="F109" s="11" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="G109" s="11" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="H109" s="11" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L109" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M109" s="9" t="n">
         <v>0.77</v>
       </c>
-      <c r="N109" s="8" t="inlineStr">
+      <c r="N109" s="12" t="inlineStr">
         <is>
           <t>2025: $3,443.4M | 2024: $3,345.9M | 2023: $3,480.6M | 2022: $3,773.0M</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="12" t="inlineStr">
         <is>
           <t>2025: $-165.3M | 2024: $-5.6M | 2023: $111.1M | 2022: $107.4M</t>
         </is>
       </c>
-      <c r="P109" s="8" t="inlineStr">
+      <c r="P109" s="12" t="inlineStr">
         <is>
           <t>Nufarm Limited, together with its subsidiaries, develops, manufactures, and sells crop protection solutions and seed technologies in Europe, the Middle East, Africa, North America, and the Asia Pacific. The company operates through Crop Protection and Seed Technologies segments. The company offers herbicides, insecticides, and fungicides that help growers protect crops against weeds, pests, and...</t>
         </is>
       </c>
-      <c r="Q109" s="5" t="inlineStr">
-        <is>
-          <t>2026-10-27 00:01</t>
+      <c r="Q109" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8325,22 +8325,22 @@
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>17.22</v>
+        <v>17.69</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>32.35</v>
+        <v>31.84</v>
       </c>
       <c r="E110" s="10" t="n">
         <v>14.57</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>0.0765</v>
+        <v>0.0678</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>0.1529</v>
+        <v>0.1356</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>0.3059</v>
+        <v>0.2712</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -8348,13 +8348,13 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>71.75</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>26.09</v>
+        <v>26.8</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>10.86</v>
+        <v>11.16</v>
       </c>
       <c r="M110" s="9" t="n">
         <v>0.43</v>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="C111" s="10" t="n">
-        <v>47.71</v>
+        <v>46.85</v>
       </c>
       <c r="D111" s="10" t="n">
         <v>49.31</v>
@@ -8401,13 +8401,13 @@
         <v>36.01</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>0.0382</v>
+        <v>0.0429</v>
       </c>
       <c r="G111" s="11" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0858</v>
       </c>
       <c r="H111" s="11" t="n">
-        <v>0.1527</v>
+        <v>0.1717</v>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
@@ -8415,13 +8415,13 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>31.39</v>
+        <v>31.23</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="M111" s="9" t="n">
         <v>0.32</v>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Q111" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>5.74</v>
+        <v>6.15</v>
       </c>
       <c r="D112" s="10" t="n">
         <v>16.78</v>
@@ -8468,13 +8468,13 @@
         <v>5.07</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>0.2261</v>
+        <v>0.1944</v>
       </c>
       <c r="G112" s="11" t="n">
-        <v>0.4522</v>
+        <v>0.3887</v>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0.9044</v>
+        <v>0.7775</v>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>47.83</v>
+        <v>51.25</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>8.789999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="M112" s="9" t="n">
         <v>0.55</v>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="C113" s="6" t="n">
-        <v>1.502</v>
+        <v>1.522</v>
       </c>
       <c r="D113" s="6" t="n">
         <v>2.43</v>
@@ -8535,13 +8535,13 @@
         <v>1.212</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>0.0235</v>
+        <v>0.0199</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.0471</v>
+        <v>0.0399</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0798</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -8549,13 +8549,13 @@
         </is>
       </c>
       <c r="J113" s="5" t="n">
-        <v>13.11</v>
+        <v>13.28</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="M113" s="5" t="n">
         <v>0.6</v>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="C114" s="6" t="n">
-        <v>12.08</v>
+        <v>12.07</v>
       </c>
       <c r="D114" s="6" t="n">
         <v>12.84</v>
@@ -8602,13 +8602,13 @@
         <v>10.02</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0025</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>0.0038</v>
+        <v>0.0049</v>
       </c>
       <c r="H114" s="7" t="n">
-        <v>0.0075</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="J114" s="5" t="n">
-        <v>13.27</v>
+        <v>13.26</v>
       </c>
       <c r="K114" s="5" t="n">
         <v>2.05</v>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="Q114" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8669,13 +8669,13 @@
         <v>18.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>0.0374</v>
+        <v>0.0363</v>
       </c>
       <c r="G115" s="11" t="n">
-        <v>0.0747</v>
+        <v>0.0727</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>0.1494</v>
+        <v>0.1453</v>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>44.27</v>
+        <v>43.42</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>2.8</v>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="Q115" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="Q116" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="C117" s="6" t="n">
-        <v>2.765</v>
+        <v>3.08</v>
       </c>
       <c r="D117" s="6" t="n">
         <v>6.81</v>
@@ -8813,13 +8813,13 @@
         <v>2.61</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>0.1604</v>
+        <v>0.1184</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>0.3208</v>
+        <v>0.2368</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.4737</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="J117" s="5" t="n">
-        <v>16.26</v>
+        <v>19.25</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>2.19</v>
+        <v>2.43</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>4.61</v>
+        <v>5.14</v>
       </c>
       <c r="M117" s="5" t="n">
         <v>0.3</v>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8871,22 +8871,22 @@
         </is>
       </c>
       <c r="C118" s="6" t="n">
-        <v>196.97</v>
+        <v>198.87</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>286.76</v>
+        <v>283.89</v>
       </c>
       <c r="E118" s="6" t="n">
         <v>107.75</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>0.0072</v>
+        <v>0.0047</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>0.0143</v>
+        <v>0.0094</v>
       </c>
       <c r="H118" s="7" t="n">
-        <v>0.0286</v>
+        <v>0.0188</v>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
@@ -8894,13 +8894,13 @@
         </is>
       </c>
       <c r="J118" s="5" t="n">
-        <v>76.64</v>
+        <v>79.55</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>45.64</v>
+        <v>46.08</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>78.63</v>
+        <v>79.39</v>
       </c>
       <c r="M118" s="5" t="n">
         <v>0.49</v>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Q118" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="C119" s="6" t="n">
-        <v>13.67</v>
+        <v>13.65</v>
       </c>
       <c r="D119" s="6" t="n">
         <v>18.74</v>
@@ -8947,13 +8947,13 @@
         <v>10.58</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>0.0317</v>
+        <v>0.0322</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.0635</v>
+        <v>0.0643</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.127</v>
+        <v>0.1286</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="J119" s="5" t="n">
-        <v>17.09</v>
+        <v>17.28</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="L119" s="5" t="n">
         <v>2.7</v>
@@ -8974,12 +8974,12 @@
       </c>
       <c r="N119" s="8" t="inlineStr">
         <is>
-          <t>2024: $1,596.6M | 2023: $1,643.5M | 2022: $1,497.5M</t>
+          <t>2026: $830.6M | 2024: $1,596.6M | 2023: $1,643.5M | 2022: $1,497.5M</t>
         </is>
       </c>
       <c r="O119" s="8" t="inlineStr">
         <is>
-          <t>2024: $257.9M | 2023: $271.1M | 2022: $285.2M</t>
+          <t>2026: $129.2M | 2024: $257.9M | 2023: $271.1M | 2022: $285.2M</t>
         </is>
       </c>
       <c r="P119" s="8" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="C120" s="6" t="n">
-        <v>17.22</v>
+        <v>17.3</v>
       </c>
       <c r="D120" s="6" t="n">
         <v>20.35</v>
@@ -9014,13 +9014,13 @@
         <v>15.1</v>
       </c>
       <c r="F120" s="7" t="n">
-        <v>0.0078</v>
+        <v>0.0066</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>0.0157</v>
+        <v>0.0133</v>
       </c>
       <c r="H120" s="7" t="n">
-        <v>0.0314</v>
+        <v>0.0266</v>
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
@@ -9028,13 +9028,13 @@
         </is>
       </c>
       <c r="J120" s="5" t="n">
-        <v>33.76</v>
+        <v>34.6</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="M120" s="5" t="n">
         <v>0.48</v>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="C121" s="10" t="n">
-        <v>8.494999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D121" s="10" t="n">
         <v>11.09</v>
@@ -9081,13 +9081,13 @@
         <v>8.035</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>0.0856</v>
+        <v>0.0743</v>
       </c>
       <c r="G121" s="11" t="n">
-        <v>0.1712</v>
+        <v>0.1487</v>
       </c>
       <c r="H121" s="11" t="n">
-        <v>0.3424</v>
+        <v>0.2974</v>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>8.539999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="M121" s="9" t="n">
         <v>6.88</v>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="Q121" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="C122" s="6" t="n">
-        <v>26.1</v>
+        <v>25.57</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>26.58</v>
@@ -9148,13 +9148,13 @@
         <v>18.57</v>
       </c>
       <c r="F122" s="7" t="n">
-        <v>-0.0111</v>
+        <v>-0.0062</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>-0.0222</v>
+        <v>-0.0123</v>
       </c>
       <c r="H122" s="7" t="n">
-        <v>-0.0444</v>
+        <v>-0.0246</v>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
@@ -9162,13 +9162,13 @@
         </is>
       </c>
       <c r="J122" s="5" t="n">
-        <v>12.49</v>
+        <v>12.18</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="M122" s="5" t="n">
         <v>0.38</v>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="C124" s="6" t="n">
-        <v>161.57</v>
+        <v>161.07</v>
       </c>
       <c r="D124" s="6" t="n">
         <v>223.28</v>
@@ -9282,13 +9282,13 @@
         <v>131.07</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0373</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>0.0757</v>
+        <v>0.0746</v>
       </c>
       <c r="H124" s="7" t="n">
-        <v>0.1514</v>
+        <v>0.1492</v>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
@@ -9296,13 +9296,13 @@
         </is>
       </c>
       <c r="J124" s="5" t="n">
-        <v>31.62</v>
+        <v>32.61</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>11.13</v>
+        <v>11.09</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>10.7</v>
+        <v>10.66</v>
       </c>
       <c r="M124" s="5" t="n">
         <v>3.96</v>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="Q124" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="C125" s="6" t="n">
-        <v>54.92</v>
+        <v>55.49</v>
       </c>
       <c r="D125" s="6" t="n">
         <v>55.98</v>
@@ -9349,13 +9349,13 @@
         <v>30.39</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.0128</v>
+        <v>-0.0152</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.0256</v>
+        <v>-0.0305</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>-0.0512</v>
+        <v>-0.0609</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
@@ -9363,13 +9363,13 @@
         </is>
       </c>
       <c r="J125" s="5" t="n">
-        <v>40.38</v>
+        <v>40.5</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M125" s="5" t="n">
         <v>1.97</v>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="C126" s="6" t="n">
-        <v>148.85</v>
+        <v>151.55</v>
       </c>
       <c r="D126" s="6" t="n">
         <v>195.84</v>
@@ -9416,13 +9416,13 @@
         <v>125.5</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>0.0318</v>
+        <v>0.0263</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>0.0636</v>
+        <v>0.0526</v>
       </c>
       <c r="H126" s="7" t="n">
-        <v>0.1272</v>
+        <v>0.1051</v>
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
@@ -9430,13 +9430,13 @@
         </is>
       </c>
       <c r="J126" s="5" t="n">
-        <v>13.63</v>
+        <v>13.57</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>3.92</v>
+        <v>3.99</v>
       </c>
       <c r="M126" s="5" t="n">
         <v>0.32</v>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="Q126" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9474,22 +9474,22 @@
         </is>
       </c>
       <c r="C127" s="10" t="n">
-        <v>35.89</v>
+        <v>35.64</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>40.19</v>
+        <v>40.08</v>
       </c>
       <c r="E127" s="10" t="n">
         <v>25.5</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>0.0299</v>
+        <v>0.0313</v>
       </c>
       <c r="G127" s="11" t="n">
-        <v>0.0597</v>
+        <v>0.0626</v>
       </c>
       <c r="H127" s="11" t="n">
-        <v>0.1195</v>
+        <v>0.1253</v>
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
@@ -9497,13 +9497,13 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>23.31</v>
+        <v>23.29</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M127" s="9" t="n">
         <v>0.13</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="Q127" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="C128" s="6" t="n">
-        <v>6.32</v>
+        <v>6.51</v>
       </c>
       <c r="D128" s="6" t="n">
         <v>10</v>
@@ -9550,13 +9550,13 @@
         <v>5.335</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>0.0557</v>
+        <v>0.0468</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>0.1114</v>
+        <v>0.0936</v>
       </c>
       <c r="H128" s="7" t="n">
-        <v>0.2228</v>
+        <v>0.1871</v>
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
@@ -9564,13 +9564,13 @@
         </is>
       </c>
       <c r="J128" s="5" t="n">
-        <v>7.02</v>
+        <v>7.23</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="M128" s="5" t="n">
         <v>4.66</v>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="Q128" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="C129" s="6" t="n">
-        <v>4.35</v>
+        <v>4.285</v>
       </c>
       <c r="D129" s="6" t="n">
         <v>4.79</v>
@@ -9617,13 +9617,13 @@
         <v>2.86</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>0.0233</v>
+        <v>0.0274</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0.0465</v>
+        <v>0.0548</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>0.0931</v>
+        <v>0.1096</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
@@ -9631,13 +9631,13 @@
         </is>
       </c>
       <c r="J129" s="5" t="n">
-        <v>435</v>
+        <v>428.5</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="M129" s="5" t="n">
         <v>0.29</v>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="C130" s="6" t="n">
-        <v>4.295</v>
+        <v>4.49</v>
       </c>
       <c r="D130" s="6" t="n">
         <v>5.33</v>
@@ -9684,13 +9684,13 @@
         <v>2.96</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>0.0465</v>
+        <v>0.0331</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>0.093</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H130" s="7" t="n">
-        <v>0.186</v>
+        <v>0.1324</v>
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
@@ -9698,13 +9698,13 @@
         </is>
       </c>
       <c r="J130" s="5" t="n">
-        <v>11.93</v>
+        <v>12.47</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>3.24</v>
+        <v>3.39</v>
       </c>
       <c r="M130" s="5" t="n">
         <v>0.19</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
         </is>
       </c>
       <c r="C131" s="6" t="n">
-        <v>3.505</v>
+        <v>3.52</v>
       </c>
       <c r="D131" s="6" t="n">
         <v>4.27</v>
@@ -9751,13 +9751,13 @@
         <v>3.275</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>0.0351</v>
+        <v>0.0338</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>0.0701</v>
+        <v>0.0677</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.1402</v>
+        <v>0.1354</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
@@ -9765,13 +9765,13 @@
         </is>
       </c>
       <c r="J131" s="5" t="n">
-        <v>9.220000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>7.12</v>
+        <v>7.15</v>
       </c>
       <c r="M131" s="5" t="n">
         <v>0.72</v>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="C132" s="6" t="n">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="D132" s="6" t="n">
         <v>8.699999999999999</v>
@@ -9837,10 +9837,10 @@
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="M132" s="5" t="n">
         <v>2.07</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="C133" s="6" t="n">
-        <v>5.795</v>
+        <v>5.8</v>
       </c>
       <c r="D133" s="6" t="n">
         <v>6.665</v>
@@ -9887,13 +9887,13 @@
         <v>3.87</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>0.0067</v>
+        <v>0.0065</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.0134</v>
+        <v>0.0129</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.0267</v>
+        <v>0.0259</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         </is>
       </c>
       <c r="J133" s="5" t="n">
-        <v>24.15</v>
+        <v>24.17</v>
       </c>
       <c r="K133" s="5" t="n">
         <v>2.72</v>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>13.38</v>
+        <v>13.43</v>
       </c>
       <c r="D134" s="10" t="n">
         <v>28.2</v>
@@ -9954,13 +9954,13 @@
         <v>10.86</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>0.1044</v>
+        <v>0.1031</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>0.2088</v>
+        <v>0.2062</v>
       </c>
       <c r="H134" s="11" t="n">
-        <v>0.4176</v>
+        <v>0.4123</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>19.11</v>
+        <v>19.18</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="M134" s="9" t="n">
         <v>0.6</v>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10012,22 +10012,22 @@
         </is>
       </c>
       <c r="C135" s="6" t="n">
-        <v>19.795</v>
+        <v>20.17</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>31.81</v>
       </c>
       <c r="E135" s="6" t="n">
-        <v>14.305</v>
+        <v>14.46</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>0.0911</v>
+        <v>0.0847</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>0.1821</v>
+        <v>0.1694</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.3643</v>
+        <v>0.3389</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="J135" s="5" t="n">
-        <v>15.84</v>
+        <v>15.76</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="M135" s="5" t="n">
         <v>0.31</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>4.19</v>
+        <v>4.235</v>
       </c>
       <c r="D136" s="10" t="n">
         <v>6.73</v>
@@ -10088,13 +10088,13 @@
         <v>3.71</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>0.0483</v>
+        <v>0.0451</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="H136" s="11" t="n">
-        <v>0.1933</v>
+        <v>0.1806</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
@@ -10102,13 +10102,13 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>10.22</v>
+        <v>10.33</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="M136" s="9" t="n">
         <v>0.47</v>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="Q136" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="C137" s="6" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="D137" s="6" t="n">
         <v>0.195</v>
@@ -10155,13 +10155,13 @@
         <v>0.083</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.0278</v>
+        <v>-0.0192</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.0556</v>
+        <v>-0.0385</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.1111</v>
+        <v>-0.0769</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -10169,13 +10169,13 @@
         </is>
       </c>
       <c r="J137" s="5" t="n">
-        <v>-12.31</v>
+        <v>-11.85</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="M137" s="5" t="n">
         <v>1.51</v>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
         </is>
       </c>
       <c r="C138" s="6" t="n">
-        <v>18.89</v>
+        <v>19.11</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>24.27</v>
@@ -10222,13 +10222,13 @@
         <v>18.11</v>
       </c>
       <c r="F138" s="7" t="n">
-        <v>0.0427</v>
+        <v>0.0393</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>0.0854</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="H138" s="7" t="n">
-        <v>0.1709</v>
+        <v>0.1574</v>
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
@@ -10236,13 +10236,13 @@
         </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>15.23</v>
+        <v>15.41</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="M138" s="5" t="n">
         <v>0.6899999999999999</v>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="Q138" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="Q139" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="C140" s="6" t="n">
-        <v>45.61</v>
+        <v>45.97</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>49.43</v>
@@ -10364,13 +10364,13 @@
         <v>34.78</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>-0.0239</v>
+        <v>-0.0257</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>-0.0478</v>
+        <v>-0.0513</v>
       </c>
       <c r="H140" s="7" t="n">
-        <v>-0.0956</v>
+        <v>-0.1027</v>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
@@ -10378,13 +10378,13 @@
         </is>
       </c>
       <c r="J140" s="5" t="n">
-        <v>7.81</v>
+        <v>7.86</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="M140" s="5" t="n">
         <v>6.55</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="Q140" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="C141" s="10" t="n">
-        <v>9.215</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="D141" s="10" t="n">
         <v>9.359999999999999</v>
@@ -10431,13 +10431,13 @@
         <v>5.9</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0131</v>
       </c>
       <c r="G141" s="11" t="n">
-        <v>0.0171</v>
+        <v>0.0261</v>
       </c>
       <c r="H141" s="11" t="n">
-        <v>0.0342</v>
+        <v>0.0523</v>
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>27.92</v>
+        <v>27.39</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="L141" s="9" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="Q141" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="C142" s="6" t="n">
-        <v>13.6</v>
+        <v>13.435</v>
       </c>
       <c r="D142" s="6" t="n">
         <v>17.65</v>
@@ -10500,13 +10500,13 @@
         <v>10.08</v>
       </c>
       <c r="F142" s="7" t="n">
-        <v>0.0196</v>
+        <v>0.0229</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>0.0392</v>
+        <v>0.0459</v>
       </c>
       <c r="H142" s="7" t="n">
-        <v>0.0785</v>
+        <v>0.0917</v>
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
@@ -10514,13 +10514,13 @@
         </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>14.95</v>
+        <v>15.1</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="M142" s="5" t="n">
         <v>1.02</v>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="Q142" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="C143" s="6" t="n">
-        <v>20.14</v>
+        <v>19.89</v>
       </c>
       <c r="D143" s="6" t="n">
         <v>20.52</v>
@@ -10567,13 +10567,13 @@
         <v>13.8</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>-0.0057</v>
+        <v>-0.0027</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>-0.0115</v>
+        <v>-0.0054</v>
       </c>
       <c r="H143" s="7" t="n">
-        <v>-0.023</v>
+        <v>-0.0107</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
@@ -10581,13 +10581,13 @@
         </is>
       </c>
       <c r="J143" s="5" t="n">
-        <v>21.66</v>
+        <v>20.72</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M143" s="5" t="n">
         <v>0.26</v>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="Q144" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="C145" s="6" t="n">
-        <v>0.845</v>
+        <v>0.84</v>
       </c>
       <c r="D145" s="6" t="n">
         <v>1.19</v>
@@ -10709,13 +10709,13 @@
         <v>0.66</v>
       </c>
       <c r="F145" s="7" t="n">
-        <v>0.0489</v>
+        <v>0.0507</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>0.0979</v>
+        <v>0.1015</v>
       </c>
       <c r="H145" s="7" t="n">
-        <v>0.1958</v>
+        <v>0.2029</v>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="J145" s="5" t="n">
-        <v>42.25</v>
+        <v>42</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="L145" s="5" t="n">
         <v>0.73</v>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10767,7 @@
         </is>
       </c>
       <c r="C146" s="6" t="n">
-        <v>13.98</v>
+        <v>13.935</v>
       </c>
       <c r="D146" s="6" t="n">
         <v>15.62</v>
@@ -10776,13 +10776,13 @@
         <v>12.82</v>
       </c>
       <c r="F146" s="7" t="n">
-        <v>-0.0053</v>
+        <v>-0.0045</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>-0.0107</v>
+        <v>-0.0091</v>
       </c>
       <c r="H146" s="7" t="n">
-        <v>-0.0213</v>
+        <v>-0.0181</v>
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
@@ -10790,13 +10790,13 @@
         </is>
       </c>
       <c r="J146" s="5" t="n">
-        <v>116.5</v>
+        <v>116.13</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>11.2</v>
+        <v>11.16</v>
       </c>
       <c r="M146" s="5" t="n">
         <v>2.71</v>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="Q146" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="C147" s="6" t="n">
-        <v>4.915</v>
+        <v>4.89</v>
       </c>
       <c r="D147" s="6" t="n">
         <v>5.58</v>
@@ -10843,13 +10843,13 @@
         <v>4.56</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>0.0049</v>
+        <v>0.0062</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0125</v>
       </c>
       <c r="H147" s="7" t="n">
-        <v>0.0197</v>
+        <v>0.0249</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="J147" s="5" t="n">
-        <v>24.57</v>
+        <v>24.45</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="M147" s="5" t="n">
         <v>1.26</v>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10901,22 +10901,22 @@
         </is>
       </c>
       <c r="C148" s="6" t="n">
-        <v>32.32</v>
+        <v>32.56</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>39.13</v>
+        <v>38.96</v>
       </c>
       <c r="E148" s="6" t="n">
         <v>20.14</v>
       </c>
       <c r="F148" s="7" t="n">
-        <v>-0.0091</v>
+        <v>-0.0109</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>-0.0183</v>
+        <v>-0.0218</v>
       </c>
       <c r="H148" s="7" t="n">
-        <v>-0.0365</v>
+        <v>-0.0436</v>
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
@@ -10924,13 +10924,13 @@
         </is>
       </c>
       <c r="J148" s="5" t="n">
-        <v>73.45</v>
+        <v>77.52</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>24.67</v>
+        <v>24.85</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>16.76</v>
+        <v>16.89</v>
       </c>
       <c r="M148" s="5" t="n">
         <v>0.12</v>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="Q148" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="C149" s="6" t="n">
-        <v>3.835</v>
+        <v>3.82</v>
       </c>
       <c r="D149" s="6" t="n">
         <v>5.85</v>
@@ -10977,13 +10977,13 @@
         <v>3.47</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>0.0168</v>
+        <v>0.0178</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>0.0336</v>
+        <v>0.0357</v>
       </c>
       <c r="H149" s="7" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
@@ -10991,13 +10991,13 @@
         </is>
       </c>
       <c r="J149" s="5" t="n">
-        <v>127.83</v>
+        <v>127.33</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="L149" s="5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M149" s="5" t="n">
         <v>0.49</v>
@@ -11019,7 +11019,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11035,22 +11035,22 @@
         </is>
       </c>
       <c r="C150" s="6" t="n">
-        <v>5.81</v>
+        <v>5.91</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>6.23</v>
+        <v>6.2</v>
       </c>
       <c r="E150" s="6" t="n">
         <v>3.34</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>0.0231</v>
+        <v>0.0185</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>0.0462</v>
+        <v>0.037</v>
       </c>
       <c r="H150" s="7" t="n">
-        <v>0.0925</v>
+        <v>0.074</v>
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
@@ -11058,13 +11058,13 @@
         </is>
       </c>
       <c r="J150" s="5" t="n">
-        <v>13.93</v>
+        <v>14.17</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="L150" s="5" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="M150" s="5" t="n">
         <v>0.6</v>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="Q150" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="C151" s="6" t="n">
-        <v>2.415</v>
+        <v>2.425</v>
       </c>
       <c r="D151" s="6" t="n">
         <v>2.73</v>
@@ -11111,13 +11111,13 @@
         <v>2.21</v>
       </c>
       <c r="F151" s="7" t="n">
-        <v>0.0183</v>
+        <v>0.0172</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>0.0366</v>
+        <v>0.0343</v>
       </c>
       <c r="H151" s="7" t="n">
-        <v>0.0731</v>
+        <v>0.0687</v>
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
@@ -11125,13 +11125,13 @@
         </is>
       </c>
       <c r="J151" s="5" t="n">
-        <v>8.050000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M151" s="5" t="n">
         <v>0.41</v>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>2.885</v>
+        <v>2.825</v>
       </c>
       <c r="D152" s="6" t="n">
         <v>3.28</v>
@@ -11178,13 +11178,13 @@
         <v>1.695</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>0.0234</v>
+        <v>0.0293</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>0.0469</v>
+        <v>0.0585</v>
       </c>
       <c r="H152" s="7" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.117</v>
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
@@ -11192,10 +11192,10 @@
         </is>
       </c>
       <c r="J152" s="5" t="n">
-        <v>20.61</v>
+        <v>21.73</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="L152" s="5" t="n">
         <v>0.16</v>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="Q152" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
         </is>
       </c>
       <c r="C153" s="6" t="n">
-        <v>36.25</v>
+        <v>36.46</v>
       </c>
       <c r="D153" s="6" t="n">
         <v>43.32</v>
@@ -11245,13 +11245,13 @@
         <v>33.46</v>
       </c>
       <c r="F153" s="7" t="n">
-        <v>-0.0204</v>
+        <v>-0.0218</v>
       </c>
       <c r="G153" s="7" t="n">
-        <v>-0.0409</v>
+        <v>-0.0435</v>
       </c>
       <c r="H153" s="7" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
@@ -11259,13 +11259,13 @@
         </is>
       </c>
       <c r="J153" s="5" t="n">
-        <v>18.03</v>
+        <v>18.14</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="Q153" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>3.515</v>
+        <v>3.58</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>5.04</v>
@@ -11314,13 +11314,13 @@
         <v>2.17</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>0.0741</v>
+        <v>0.0682</v>
       </c>
       <c r="G154" s="11" t="n">
-        <v>0.1481</v>
+        <v>0.1363</v>
       </c>
       <c r="H154" s="11" t="n">
-        <v>0.2962</v>
+        <v>0.2727</v>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
@@ -11328,13 +11328,13 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>35.15</v>
+        <v>35.8</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="L154" s="9" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="M154" s="9" t="n">
         <v>0.44</v>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="Q154" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
         </is>
       </c>
       <c r="C155" s="6" t="n">
-        <v>78.76000000000001</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="D155" s="6" t="n">
         <v>94.7</v>
@@ -11381,13 +11381,13 @@
         <v>70.8</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>-0.0165</v>
+        <v>-0.0158</v>
       </c>
       <c r="H155" s="7" t="n">
-        <v>-0.0329</v>
+        <v>-0.0316</v>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
@@ -11395,10 +11395,10 @@
         </is>
       </c>
       <c r="J155" s="5" t="n">
-        <v>31.63</v>
+        <v>31.09</v>
       </c>
       <c r="K155" s="5" t="n">
-        <v>11.21</v>
+        <v>11.19</v>
       </c>
       <c r="L155" s="5" t="n">
         <v>1.89</v>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="Q155" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="C156" s="6" t="n">
-        <v>7.975</v>
+        <v>7.87</v>
       </c>
       <c r="D156" s="6" t="n">
         <v>9.9</v>
@@ -11448,13 +11448,13 @@
         <v>6.66</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>0.0242</v>
+        <v>0.0279</v>
       </c>
       <c r="G156" s="7" t="n">
-        <v>0.0484</v>
+        <v>0.0557</v>
       </c>
       <c r="H156" s="7" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1114</v>
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
@@ -11462,13 +11462,13 @@
         </is>
       </c>
       <c r="J156" s="5" t="n">
-        <v>16.61</v>
+        <v>16.06</v>
       </c>
       <c r="K156" s="5" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M156" s="5" t="n">
         <v>0.39</v>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="Q156" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11506,33 +11506,33 @@
         </is>
       </c>
       <c r="C157" s="6" t="n">
-        <v>9.645</v>
+        <v>9.73</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>14.615</v>
+        <v>14.57</v>
       </c>
       <c r="E157" s="6" t="n">
         <v>9.1</v>
       </c>
       <c r="F157" s="7" t="n">
-        <v>0.0525</v>
+        <v>0.0476</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>0.105</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="H157" s="7" t="n">
-        <v>0.21</v>
+        <v>0.1903</v>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>20.52</v>
+        <v>20.7</v>
       </c>
       <c r="K157" s="5" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="L157" s="5" t="n">
         <v>0.44</v>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="Q157" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="C158" s="6" t="n">
-        <v>40.58</v>
+        <v>41.21</v>
       </c>
       <c r="D158" s="6" t="n">
         <v>42</v>
@@ -11582,13 +11582,13 @@
         <v>26.36</v>
       </c>
       <c r="F158" s="7" t="n">
-        <v>-0.0073</v>
+        <v>-0.011</v>
       </c>
       <c r="G158" s="7" t="n">
-        <v>-0.0145</v>
+        <v>-0.022</v>
       </c>
       <c r="H158" s="7" t="n">
-        <v>-0.0291</v>
+        <v>-0.0439</v>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
@@ -11596,10 +11596,10 @@
         </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>44.59</v>
+        <v>44.31</v>
       </c>
       <c r="K158" s="5" t="n">
-        <v>10.32</v>
+        <v>10.48</v>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="Q158" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="C159" s="6" t="n">
-        <v>33.34</v>
+        <v>32.715</v>
       </c>
       <c r="D159" s="6" t="n">
         <v>35.82</v>
@@ -11651,13 +11651,13 @@
         <v>22.25</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>0.007</v>
+        <v>0.0114</v>
       </c>
       <c r="G159" s="7" t="n">
-        <v>0.0139</v>
+        <v>0.0228</v>
       </c>
       <c r="H159" s="7" t="n">
-        <v>0.0278</v>
+        <v>0.0455</v>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
@@ -11665,13 +11665,13 @@
         </is>
       </c>
       <c r="J159" s="5" t="n">
-        <v>13.95</v>
+        <v>13.75</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>4.58</v>
+        <v>4.49</v>
       </c>
       <c r="M159" s="5" t="n">
         <v>0.33</v>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="Q159" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="C160" s="6" t="n">
-        <v>2.115</v>
+        <v>2.11</v>
       </c>
       <c r="D160" s="6" t="n">
         <v>2.73</v>
@@ -11718,13 +11718,13 @@
         <v>2.005</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>0.0615</v>
+        <v>0.0622</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>0.123</v>
+        <v>0.1244</v>
       </c>
       <c r="H160" s="7" t="n">
-        <v>0.2459</v>
+        <v>0.2489</v>
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="J160" s="5" t="n">
-        <v>11.13</v>
+        <v>11.11</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>132.19</v>
+        <v>131.87</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>17.24</v>
+        <v>17.2</v>
       </c>
       <c r="M160" s="5" t="n">
         <v>0.49</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="Q160" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11776,22 +11776,22 @@
         </is>
       </c>
       <c r="C161" s="10" t="n">
-        <v>40.26</v>
+        <v>40.81</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>86.92</v>
+        <v>79.09</v>
       </c>
       <c r="E161" s="10" t="n">
         <v>28.76</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>0.1132</v>
+        <v>0.1078</v>
       </c>
       <c r="G161" s="11" t="n">
-        <v>0.2264</v>
+        <v>0.2156</v>
       </c>
       <c r="H161" s="11" t="n">
-        <v>0.4528</v>
+        <v>0.4311</v>
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
@@ -11799,13 +11799,13 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>50.32</v>
+        <v>52.32</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>4.86</v>
+        <v>4.92</v>
       </c>
       <c r="L161" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="M161" s="9" t="n">
         <v>1.15</v>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="Q161" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>63.63</v>
+        <v>64.06</v>
       </c>
       <c r="D162" s="10" t="n">
         <v>154.26</v>
@@ -11852,13 +11852,13 @@
         <v>55.09</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>0.2303</v>
+        <v>0.2257</v>
       </c>
       <c r="G162" s="11" t="n">
-        <v>0.4606</v>
+        <v>0.4514</v>
       </c>
       <c r="H162" s="11" t="n">
-        <v>0.9211</v>
+        <v>0.9028</v>
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
@@ -11866,13 +11866,13 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>33.59</v>
+        <v>33.82</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="L162" s="9" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="M162" s="9" t="n">
         <v>0.39</v>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="Q162" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -11910,22 +11910,22 @@
         </is>
       </c>
       <c r="C163" s="10" t="n">
-        <v>1.717</v>
+        <v>1.77</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>4.21</v>
+        <v>4.125</v>
       </c>
       <c r="E163" s="10" t="n">
         <v>1.025</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>0.2863</v>
+        <v>0.2644</v>
       </c>
       <c r="G163" s="11" t="n">
-        <v>0.5726</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="H163" s="11" t="n">
-        <v>1.1452</v>
+        <v>1.0574</v>
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
@@ -11933,13 +11933,13 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>17.17</v>
+        <v>17.7</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="L163" s="9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M163" s="9" t="n">
         <v>4.09</v>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="Q163" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>0.43</v>
@@ -12109,13 +12109,13 @@
         <v>0.11</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0.1167</v>
+        <v>0.0688</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.1377</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>0.4666</v>
+        <v>0.2753</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="J2" s="9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="L2" s="9" t="n">
-        <v>36.27</v>
+        <v>41.72</v>
       </c>
       <c r="M2" s="9" t="n">
         <v>9.02</v>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.675</v>
+        <v>0.725</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2.65</v>
@@ -12251,13 +12251,13 @@
         <v>0.635</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>0.1601</v>
+        <v>0.1319</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.3203</v>
+        <v>0.2637</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.5274</v>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
@@ -12265,13 +12265,13 @@
         </is>
       </c>
       <c r="J4" s="5" t="n">
-        <v>22.5</v>
+        <v>24.17</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>3.37</v>
+        <v>3.62</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0.34</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0.16</v>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>63.32</v>
+        <v>69.87</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.36</v>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12378,22 +12378,22 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.215</v>
+        <v>0.205</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0.105</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2.5011</v>
+        <v>2.4221</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>5.0023</v>
+        <v>4.8443</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>10.0045</v>
+        <v>9.688599999999999</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -12401,13 +12401,13 @@
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-9.4</v>
+        <v>-9.66</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>122.88</v>
+        <v>126.32</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>2.95</v>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12445,22 +12445,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>0.032</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.3472</v>
+        <v>1.3041</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>2.6944</v>
+        <v>2.6081</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5.3889</v>
+        <v>5.2162</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.93</v>
+        <v>-0.96</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>9.56</v>
+        <v>9.83</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.7</v>
@@ -12496,7 +12496,7 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12512,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>5.39</v>
+        <v>5.885</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>6.96</v>
@@ -12521,13 +12521,13 @@
         <v>4.42</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.0641</v>
+        <v>0.0407</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.1281</v>
+        <v>0.0814</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.2563</v>
+        <v>0.1628</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
@@ -12535,13 +12535,13 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>11.23</v>
+        <v>13.08</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>4.82</v>
+        <v>5.26</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0.09</v>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.785</v>
+        <v>0.837</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>0.93</v>
@@ -12588,13 +12588,13 @@
         <v>0.405</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0366</v>
+        <v>0.0188</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.0732</v>
+        <v>0.0376</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.1465</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -12602,13 +12602,13 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>21.27</v>
+        <v>22.68</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>265.5</v>
+        <v>283.09</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>0.21</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12646,7 +12646,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>12.93</v>
+        <v>12.84</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>18.22</v>
@@ -12655,13 +12655,13 @@
         <v>8.26</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.2173</v>
+        <v>0.2206</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.4347</v>
+        <v>0.4412</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.8694</v>
+        <v>0.8825</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -12669,13 +12669,13 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>92.36</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="M10" s="9" t="n">
         <v>1.19</v>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.152</v>
+        <v>0.157</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0.49</v>
@@ -12722,13 +12722,13 @@
         <v>0.145</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0.0369</v>
+        <v>0.0273</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.0737</v>
+        <v>0.0546</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.1475</v>
+        <v>0.1093</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0.14</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>7.25</v>
+        <v>7.85</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>15.1</v>
@@ -12789,13 +12789,13 @@
         <v>6.82</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.1834</v>
+        <v>0.1496</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.3668</v>
+        <v>0.2993</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.7336</v>
+        <v>0.5986</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -12803,13 +12803,13 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>362.5</v>
+        <v>392.5</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>10.71</v>
+        <v>11.59</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>0.17</v>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:02</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>19.295</v>
+        <v>20.62</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>25</v>
@@ -12856,13 +12856,13 @@
         <v>14.41</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.0487</v>
+        <v>0.0249</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.0974</v>
+        <v>0.0499</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1948</v>
+        <v>0.0997</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -12870,13 +12870,13 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>16.49</v>
+        <v>17.93</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>5.48</v>
+        <v>5.86</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>1.65</v>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.695</v>
+        <v>0.71</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>1.21</v>
@@ -12923,13 +12923,13 @@
         <v>0.64</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.1421</v>
+        <v>0.1338</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.2841</v>
+        <v>0.2676</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.5683</v>
+        <v>0.5351</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -12937,13 +12937,13 @@
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>17.38</v>
+        <v>17.75</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>10</v>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>0.155</v>
@@ -13059,13 +13059,13 @@
         <v>0.033</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1.3125</v>
+        <v>1.3526</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>2.625</v>
+        <v>2.7051</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>5.25</v>
+        <v>5.4103</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -13073,13 +13073,13 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>1.04</v>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13117,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>0.895</v>
+        <v>0.947</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>2.63</v>
@@ -13126,13 +13126,13 @@
         <v>0.868</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.3692</v>
+        <v>0.3352</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.6704</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>1.4767</v>
+        <v>1.3407</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>-20.07</v>
+        <v>-21.23</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>3.21</v>
+        <v>3.39</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13245,74 +13245,74 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>GL1</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Global Lithium Resources Limited</t>
         </is>
       </c>
-      <c r="C19" s="10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="D19" s="10" t="n">
+      <c r="C19" s="6" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>1.08</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="6" t="n">
         <v>0.365</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>0.1011</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>0.2022</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>0.4045</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>-27.38</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="M19" s="9" t="n">
+      <c r="F19" s="7" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-27.54</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="M19" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="N19" s="12" t="inlineStr">
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>2024: $0.6M | 2023: $0.1M</t>
         </is>
       </c>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>2024: $-4.4M | 2023: $-4.4M | 2022: $-4.3M</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>Global Lithium Resources Limited engages in the evaluation, exploration, and development of lithium resources in Australia. Its flagship project is the 100% owned Manna Lithium Project located in Kalgoorlie, Western Australia. Global Lithium Resources Limited was incorporated in 2018 and is based in West Perth, Australia.</t>
         </is>
       </c>
-      <c r="Q19" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-27 00:03</t>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>0.715</v>
+        <v>0.782</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>2.97</v>
@@ -13337,13 +13337,13 @@
         <v>0.665</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.3552</v>
+        <v>0.3034</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.7104</v>
+        <v>0.6067</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>1.4209</v>
+        <v>1.2134</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -13351,13 +13351,13 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>71.5</v>
+        <v>78.2</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>93.81</v>
+        <v>102.6</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.49</v>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1.315</v>
+        <v>1.385</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>2.15</v>
@@ -13404,13 +13404,13 @@
         <v>0.995</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0477</v>
+        <v>0.0327</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0.0954</v>
+        <v>0.0653</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.1908</v>
+        <v>0.1307</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -13418,13 +13418,13 @@
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>131.5</v>
+        <v>138.5</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>3.61</v>
+        <v>3.81</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.07000000000000001</v>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:57</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>1.075</v>
@@ -13471,13 +13471,13 @@
         <v>0.155</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.725</v>
+        <v>0.6786</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1.45</v>
+        <v>1.3571</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>2.9</v>
+        <v>2.7143</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
@@ -13485,13 +13485,13 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>174.79</v>
+        <v>183.53</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0.026</v>
+        <v>0.031</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0.135</v>
@@ -13554,10 +13554,10 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>1.155</v>
+        <v>1.24</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>7.16</v>
@@ -13684,13 +13684,13 @@
         <v>1.015</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1.2652</v>
+        <v>1.1613</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>2.5303</v>
+        <v>2.3226</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>5.0606</v>
+        <v>4.6452</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-9</v>
+        <v>-9.74</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>100.67</v>
+        <v>108.07</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>5.57</v>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14036,10 +14036,10 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.079</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>0.74</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>0.07199999999999999</v>
@@ -14059,13 +14059,13 @@
         </is>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.86</v>
+        <v>-0.93</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>14.04</v>
+        <v>15.28</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>0.58</v>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="C31" s="10" t="n">
-        <v>16.99</v>
+        <v>18.375</v>
       </c>
       <c r="D31" s="10" t="n">
         <v>23.2</v>
@@ -14112,13 +14112,13 @@
         <v>6.4</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.1604</v>
+        <v>0.1294</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.3207</v>
+        <v>0.2588</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.6414</v>
+        <v>0.5177</v>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
@@ -14126,13 +14126,13 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>18.21</v>
+        <v>19.7</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>3.64</v>
+        <v>3.94</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>13.21</v>
+        <v>14.29</v>
       </c>
       <c r="M31" s="9" t="n">
         <v>0.11</v>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>8.890000000000001</v>
@@ -14179,13 +14179,13 @@
         <v>2.3</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.6816</v>
+        <v>0.6522</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>1.3633</v>
+        <v>1.3043</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>2.7265</v>
+        <v>2.6087</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -14193,13 +14193,13 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-12.89</v>
+        <v>-13.32</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>38.93</v>
+        <v>40.2</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0.24</v>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14312,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>5.16</v>
@@ -14321,13 +14321,13 @@
         <v>2.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.1263</v>
+        <v>0.1075</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.2527</v>
+        <v>0.215</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.5054</v>
+        <v>0.4299</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -14335,13 +14335,13 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>50</v>
+        <v>51.57</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>6.39</v>
+        <v>6.59</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>2.02</v>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0.325</v>
@@ -14463,13 +14463,13 @@
         <v>0.11</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.4821</v>
+        <v>0.3906</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0.9643</v>
+        <v>0.7812</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>1.9286</v>
+        <v>1.5625</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-8.24</v>
+        <v>-9.41</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>2.86</v>
+        <v>3.27</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>2018.48</v>
+        <v>2306.83</v>
       </c>
       <c r="M36" s="5" t="n">
         <v>0.44</v>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14521,22 +14521,22 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.142</v>
+        <v>0.155</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.42</v>
+        <v>0.385</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0.14</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.221</v>
+        <v>0.1815</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0.4419</v>
+        <v>0.3629</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.8838</v>
+        <v>0.7258</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         </is>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-32.2</v>
+        <v>-35.15</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14641,7 @@
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>0.142</v>
+        <v>0.152</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>0.38</v>
@@ -14741,13 +14741,13 @@
         <v>0.13</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.5423</v>
+        <v>0.4901</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>1.0845</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>2.169</v>
+        <v>1.9605</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -14760,10 +14760,10 @@
         </is>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>1043.09</v>
+        <v>1116.54</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>0.14</v>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -14929,7 +14929,7 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>0.185</v>
@@ -15100,13 +15100,13 @@
         <v>0.042</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1.0198</v>
+        <v>1.0403</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>2.0397</v>
+        <v>2.0806</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>4.0794</v>
+        <v>4.1613</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -15119,10 +15119,10 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>1140.03</v>
+        <v>1121.93</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.39</v>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:03</t>
+          <t>2026-10-27 23:58</t>
         </is>
       </c>
     </row>
